--- a/Reporte-Not-Responding.xlsx
+++ b/Reporte-Not-Responding.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\casse\Desktop\notResponding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BD7FCC-D7EB-4A1A-B1DA-8C29063EB03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8958F734-0D67-4435-B0DA-CA859B6499F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13474" xr2:uid="{B9A6FCB1-671B-4FAD-81D4-05626EB7336B}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13474" activeTab="1" xr2:uid="{B9A6FCB1-671B-4FAD-81D4-05626EB7336B}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN POR RANGO DE HORA" sheetId="2" r:id="rId1"/>
@@ -155,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -197,50 +197,11 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -714,13 +675,13 @@
                   <c:v>148</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>62</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0</c:v>
@@ -1528,7 +1489,7 @@
                   <c:v>1210</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1162</c:v>
+                  <c:v>1307</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3532,7 +3493,7 @@
                 </a:outerShdw>
               </a:effectLst>
             </a:rPr>
-            <a:t> del total de desconexiones por día </a:t>
+            <a:t> del total de Not Responding por día </a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3543,13 +3504,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Casseli Layza" refreshedDate="46133.792753703703" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="2664" xr:uid="{1C2E7FAE-0576-4AC9-AAFD-F52357483770}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Casseli Layza" refreshedDate="46133.932331249998" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="2688" xr:uid="{1C2E7FAE-0576-4AC9-AAFD-F52357483770}">
   <cacheSource type="worksheet">
     <worksheetSource name="TBRESUMEN"/>
   </cacheSource>
   <cacheFields count="6">
     <cacheField name="FECHA" numFmtId="14">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2025-12-01T00:00:00" maxDate="2026-04-22T00:00:00" count="133">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2025-12-01T00:00:00" maxDate="2026-04-22T00:00:00" count="134">
         <d v="2026-01-01T00:00:00"/>
         <d v="2026-01-02T00:00:00"/>
         <d v="2026-01-03T00:00:00"/>
@@ -3660,6 +3621,7 @@
         <d v="2026-04-18T00:00:00"/>
         <d v="2026-04-19T00:00:00"/>
         <d v="2026-04-20T00:00:00"/>
+        <m/>
         <d v="2026-04-21T00:00:00"/>
         <d v="2025-12-01T00:00:00" u="1"/>
         <d v="2025-12-02T00:00:00" u="1"/>
@@ -3686,7 +3648,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="AÑO" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2026" maxValue="2026"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2026" maxValue="2026"/>
     </cacheField>
     <cacheField name="MES" numFmtId="0">
       <sharedItems containsBlank="1" count="6">
@@ -3694,12 +3656,12 @@
         <s v="FEBRERO"/>
         <s v="MARZO"/>
         <s v="ABRIL"/>
-        <m u="1"/>
+        <m/>
         <s v="DICIEMBRE" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="DIA" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="31" count="31">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="31" count="32">
         <n v="1"/>
         <n v="2"/>
         <n v="3"/>
@@ -3731,10 +3693,11 @@
         <n v="29"/>
         <n v="30"/>
         <n v="31"/>
+        <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="HORA" numFmtId="20">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="1899-12-30T00:00:00" maxDate="1899-12-31T00:00:00" count="24">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="1899-12-30T00:00:00" maxDate="1899-12-31T00:00:00" count="25">
         <d v="1899-12-30T00:00:00"/>
         <d v="1899-12-30T01:00:00"/>
         <d v="1899-12-30T02:00:00"/>
@@ -3759,10 +3722,11 @@
         <d v="1899-12-30T21:00:00"/>
         <d v="1899-12-30T22:00:00"/>
         <d v="1899-12-30T23:00:00"/>
+        <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="Cantidad" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="555"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="555"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -3774,7 +3738,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="2664">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="2688">
   <r>
     <x v="0"/>
     <n v="2026"/>
@@ -24897,6 +24861,198 @@
   </r>
   <r>
     <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
+    <m/>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="24"/>
+    <m/>
+  </r>
+  <r>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -24904,7 +25060,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -24912,7 +25068,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -24920,7 +25076,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -24928,7 +25084,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -24936,7 +25092,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -24944,7 +25100,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -24952,7 +25108,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -24960,7 +25116,7 @@
     <n v="32"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -24968,7 +25124,7 @@
     <n v="18"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -24976,7 +25132,7 @@
     <n v="129"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -24984,7 +25140,7 @@
     <n v="125"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -24992,7 +25148,7 @@
     <n v="179"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25000,7 +25156,7 @@
     <n v="101"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25008,7 +25164,7 @@
     <n v="105"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25016,7 +25172,7 @@
     <n v="161"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25024,7 +25180,7 @@
     <n v="150"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25032,31 +25188,31 @@
     <n v="148"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
     <x v="17"/>
-    <n v="14"/>
-  </r>
-  <r>
-    <x v="110"/>
+    <n v="81"/>
+  </r>
+  <r>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
     <x v="18"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="110"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
     <x v="19"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="110"/>
+    <n v="16"/>
+  </r>
+  <r>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25064,7 +25220,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25072,7 +25228,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25080,7 +25236,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25103,12 +25259,12 @@
         <item h="1" x="2"/>
         <item x="3"/>
         <item h="1" m="1" x="5"/>
-        <item h="1" m="1" x="4"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0">
-      <items count="32">
+      <items count="33">
         <item h="1" x="0"/>
         <item h="1" x="1"/>
         <item h="1" x="2"/>
@@ -25140,11 +25296,12 @@
         <item h="1" x="28"/>
         <item h="1" x="29"/>
         <item h="1" x="30"/>
+        <item h="1" x="31"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
-      <items count="25">
+      <items count="26">
         <item x="7"/>
         <item x="8"/>
         <item x="9"/>
@@ -25169,6 +25326,7 @@
         <item x="6"/>
         <item x="4"/>
         <item x="2"/>
+        <item x="24"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -25261,16 +25419,16 @@
     <dataField name="Suma de Cantidad" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="25">
+    <format dxfId="13">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="12">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="11">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="23">
@@ -25301,10 +25459,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -25336,8 +25494,7 @@
   <location ref="H5:I27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" numFmtId="14" showAll="0">
-      <items count="134">
-        <item m="1" x="111"/>
+      <items count="135">
         <item m="1" x="112"/>
         <item m="1" x="113"/>
         <item m="1" x="114"/>
@@ -25359,6 +25516,7 @@
         <item m="1" x="130"/>
         <item m="1" x="131"/>
         <item m="1" x="132"/>
+        <item m="1" x="133"/>
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -25469,6 +25627,7 @@
         <item x="107"/>
         <item x="108"/>
         <item x="109"/>
+        <item x="111"/>
         <item x="110"/>
         <item t="default"/>
       </items>
@@ -25481,12 +25640,12 @@
         <item h="1" x="2"/>
         <item x="3"/>
         <item h="1" m="1" x="5"/>
-        <item h="1" m="1" x="4"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0">
-      <items count="32">
+      <items count="33">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -25518,6 +25677,7 @@
         <item x="28"/>
         <item x="29"/>
         <item x="30"/>
+        <item x="31"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -25649,7 +25809,7 @@
   </pivotTables>
   <data>
     <tabular pivotCacheId="1548459532">
-      <items count="31">
+      <items count="32">
         <i x="0"/>
         <i x="1"/>
         <i x="2"/>
@@ -25681,6 +25841,7 @@
         <i x="28" nd="1"/>
         <i x="29" nd="1"/>
         <i x="30" nd="1"/>
+        <i x="31" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -25714,7 +25875,7 @@
   </pivotTables>
   <data>
     <tabular pivotCacheId="1548459532">
-      <items count="31">
+      <items count="32">
         <i x="0" s="1"/>
         <i x="1" s="1"/>
         <i x="2" s="1"/>
@@ -25746,6 +25907,7 @@
         <i x="28" s="1" nd="1"/>
         <i x="29" s="1" nd="1"/>
         <i x="30" s="1" nd="1"/>
+        <i x="31" s="1" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -25787,17 +25949,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{785E938A-DD83-44EB-8612-1F46419DD23C}" name="TBRESUMEN" displayName="TBRESUMEN" ref="A5:F2669" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{785E938A-DD83-44EB-8612-1F46419DD23C}" name="TBRESUMEN" displayName="TBRESUMEN" ref="A5:F2669" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A5:F2669" xr:uid="{785E938A-DD83-44EB-8612-1F46419DD23C}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{AA03A56E-BE6E-44BD-8664-0BE5E7E8EC5C}" name="FECHA" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{F392B1E8-81BF-4618-99C5-63CFF80F9BE5}" name="AÑO" dataDxfId="16">
-      <calculatedColumnFormula>YEAR(TBRESUMEN[[#This Row],[FECHA]])</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{2CF8B524-5A6E-4C4C-8659-5EC25E28EABE}" name="MES" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{3740A5C0-233F-4752-A308-55D65365E6F0}" name="DIA" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{724991CC-97B3-4E4E-A1EB-9B8303442499}" name="HORA" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{BBD02E23-3878-488A-ADD6-68A4C8637607}" name="Cantidad" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{AA03A56E-BE6E-44BD-8664-0BE5E7E8EC5C}" name="FECHA" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{F392B1E8-81BF-4618-99C5-63CFF80F9BE5}" name="AÑO" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{2CF8B524-5A6E-4C4C-8659-5EC25E28EABE}" name="MES" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{3740A5C0-233F-4752-A308-55D65365E6F0}" name="DIA" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{724991CC-97B3-4E4E-A1EB-9B8303442499}" name="HORA" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{BBD02E23-3878-488A-ADD6-68A4C8637607}" name="Cantidad" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -25808,12 +25968,12 @@
   <autoFilter ref="A5:F1708" xr:uid="{785E938A-DD83-44EB-8612-1F46419DD23C}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{7D5CE986-03DE-4336-8DE6-10EE2FA4B5F2}" name="FECHA"/>
-    <tableColumn id="9" xr3:uid="{0FB34336-64F8-49F1-83FC-84A5CC0A6D3C}" name="AÑO" dataDxfId="27">
+    <tableColumn id="9" xr3:uid="{0FB34336-64F8-49F1-83FC-84A5CC0A6D3C}" name="AÑO" dataDxfId="15">
       <calculatedColumnFormula>YEAR(TBRESUMEN3[[#This Row],[FECHA]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{11A2B8AE-7AF3-4590-AF5E-6B075F8D4479}" name="MES"/>
     <tableColumn id="3" xr3:uid="{543B0EF0-62F6-461E-AEB3-23686CCF9AEA}" name="DIA"/>
-    <tableColumn id="4" xr3:uid="{EC35CD38-5F7B-4AC8-ADB3-30881E726247}" name="HORA" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{EC35CD38-5F7B-4AC8-ADB3-30881E726247}" name="HORA" dataDxfId="14"/>
     <tableColumn id="5" xr3:uid="{A5918A95-B5A3-4D43-B89A-E76A6B9EB015}" name="Cantidad"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -26212,7 +26372,7 @@
       <c r="H6" s="15">
         <v>0.29166666666666669</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="13">
         <v>32</v>
       </c>
     </row>
@@ -26238,7 +26398,7 @@
       <c r="H7" s="15">
         <v>0.33333333333333331</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="13">
         <v>18</v>
       </c>
     </row>
@@ -26264,7 +26424,7 @@
       <c r="H8" s="15">
         <v>0.375</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="13">
         <v>129</v>
       </c>
     </row>
@@ -26290,7 +26450,7 @@
       <c r="H9" s="15">
         <v>0.41666666666666669</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="13">
         <v>125</v>
       </c>
     </row>
@@ -26316,7 +26476,7 @@
       <c r="H10" s="15">
         <v>0.45833333333333331</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="13">
         <v>179</v>
       </c>
     </row>
@@ -26342,7 +26502,7 @@
       <c r="H11" s="15">
         <v>0.5</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="13">
         <v>101</v>
       </c>
     </row>
@@ -26368,7 +26528,7 @@
       <c r="H12" s="15">
         <v>0.54166666666666663</v>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="13">
         <v>105</v>
       </c>
     </row>
@@ -26394,7 +26554,7 @@
       <c r="H13" s="15">
         <v>0.58333333333333337</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="13">
         <v>161</v>
       </c>
     </row>
@@ -26420,7 +26580,7 @@
       <c r="H14" s="15">
         <v>0.625</v>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="13">
         <v>150</v>
       </c>
     </row>
@@ -26446,7 +26606,7 @@
       <c r="H15" s="15">
         <v>0.66666666666666663</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="13">
         <v>148</v>
       </c>
     </row>
@@ -26472,8 +26632,8 @@
       <c r="H16" s="15">
         <v>0.70833333333333337</v>
       </c>
-      <c r="I16" s="17">
-        <v>14</v>
+      <c r="I16" s="13">
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -26498,8 +26658,8 @@
       <c r="H17" s="15">
         <v>0.75</v>
       </c>
-      <c r="I17" s="17">
-        <v>0</v>
+      <c r="I17" s="13">
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -26524,8 +26684,8 @@
       <c r="H18" s="15">
         <v>0.79166666666666663</v>
       </c>
-      <c r="I18" s="17">
-        <v>0</v>
+      <c r="I18" s="13">
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -26550,7 +26710,7 @@
       <c r="H19" s="15">
         <v>0.83333333333333337</v>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="13">
         <v>0</v>
       </c>
     </row>
@@ -26576,7 +26736,7 @@
       <c r="H20" s="15">
         <v>0.875</v>
       </c>
-      <c r="I20" s="17">
+      <c r="I20" s="13">
         <v>0</v>
       </c>
     </row>
@@ -26602,7 +26762,7 @@
       <c r="H21" s="15">
         <v>0.91666666666666663</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="13">
         <v>0</v>
       </c>
     </row>
@@ -26628,7 +26788,7 @@
       <c r="H22" s="15">
         <v>0.95833333333333337</v>
       </c>
-      <c r="I22" s="17">
+      <c r="I22" s="13">
         <v>0</v>
       </c>
     </row>
@@ -26654,7 +26814,7 @@
       <c r="H23" s="15">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="13">
         <v>0</v>
       </c>
     </row>
@@ -26680,7 +26840,7 @@
       <c r="H24" s="15">
         <v>0.125</v>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="13">
         <v>0</v>
       </c>
     </row>
@@ -26706,7 +26866,7 @@
       <c r="H25" s="15">
         <v>0</v>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="13">
         <v>0</v>
       </c>
     </row>
@@ -26732,7 +26892,7 @@
       <c r="H26" s="15">
         <v>0.20833333333333334</v>
       </c>
-      <c r="I26" s="17">
+      <c r="I26" s="13">
         <v>0</v>
       </c>
     </row>
@@ -26758,7 +26918,7 @@
       <c r="H27" s="15">
         <v>0.25</v>
       </c>
-      <c r="I27" s="17">
+      <c r="I27" s="13">
         <v>0</v>
       </c>
     </row>
@@ -26784,7 +26944,7 @@
       <c r="H28" s="15">
         <v>0.16666666666666666</v>
       </c>
-      <c r="I28" s="17">
+      <c r="I28" s="13">
         <v>0</v>
       </c>
     </row>
@@ -26810,7 +26970,7 @@
       <c r="H29" s="15">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="I29" s="17">
+      <c r="I29" s="13">
         <v>0</v>
       </c>
     </row>
@@ -26836,8 +26996,8 @@
       <c r="H30" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="I30" s="17">
-        <v>1162</v>
+      <c r="I30" s="13">
+        <v>1307</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -79499,7 +79659,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="F2663" s="13">
-        <v>14</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2664" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -79519,7 +79679,7 @@
         <v>0.75</v>
       </c>
       <c r="F2664" s="13">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2665" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -79539,7 +79699,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F2665" s="13">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2666" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -79909,7 +80069,7 @@
         <v>46133</v>
       </c>
       <c r="I26">
-        <v>1162</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
@@ -79919,7 +80079,7 @@
         <v>4</v>
       </c>
       <c r="I27">
-        <v>18051</v>
+        <v>18196</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">

--- a/Reporte-Not-Responding.xlsx
+++ b/Reporte-Not-Responding.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\casse\Desktop\notResponding\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DTS WORK\SOPORTE\notResponding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8958F734-0D67-4435-B0DA-CA859B6499F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC901910-F305-409C-932F-717FF8135346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13474" activeTab="1" xr2:uid="{B9A6FCB1-671B-4FAD-81D4-05626EB7336B}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13474" xr2:uid="{B9A6FCB1-671B-4FAD-81D4-05626EB7336B}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN POR RANGO DE HORA" sheetId="2" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2684" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2948" uniqueCount="16">
   <si>
     <t>MES</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>ABRIL</t>
+  </si>
+  <si>
+    <t>MAYO</t>
   </si>
 </sst>
 </file>
@@ -155,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -197,11 +200,92 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="40">
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -244,12 +328,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -564,76 +642,76 @@
               <c:strCache>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
+                  <c:v>0:00:00</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1:00:00</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2:00:00</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3:00:00</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4:00:00</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5:00:00</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6:00:00</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>7:00:00</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="8">
                   <c:v>8:00:00</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="9">
                   <c:v>9:00:00</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="10">
                   <c:v>10:00:00</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="11">
                   <c:v>11:00:00</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="12">
                   <c:v>12:00:00</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="13">
                   <c:v>13:00:00</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="14">
                   <c:v>14:00:00</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
                   <c:v>15:00:00</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="16">
                   <c:v>16:00:00</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="17">
                   <c:v>17:00:00</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="18">
                   <c:v>18:00:00</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="19">
                   <c:v>19:00:00</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="20">
                   <c:v>20:00:00</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="21">
                   <c:v>21:00:00</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="22">
                   <c:v>22:00:00</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="23">
                   <c:v>23:00:00</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1:00:00</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>3:00:00</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0:00:00</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>5:00:00</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>6:00:00</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>4:00:00</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>2:00:00</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -645,43 +723,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>32</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>129</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>125</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>179</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>101</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>105</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>161</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>150</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>148</c:v>
+                  <c:v>136</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>81</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>62</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>16</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0</c:v>
@@ -1353,9 +1431,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'RESUMEN POR DIA'!$H$6:$H$27</c:f>
+              <c:f>'RESUMEN POR DIA'!$H$6:$H$36</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>01/04/2026</c:v>
                 </c:pt>
@@ -1419,15 +1497,42 @@
                 <c:pt idx="20">
                   <c:v>21/04/2026</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>22/04/2026</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23/04/2026</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24/04/2026</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25/04/2026</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26/04/2026</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27/04/2026</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28/04/2026</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29/04/2026</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30/04/2026</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'RESUMEN POR DIA'!$I$6:$I$27</c:f>
+              <c:f>'RESUMEN POR DIA'!$I$6:$I$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>1075</c:v>
                 </c:pt>
@@ -1490,6 +1595,33 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>1307</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1119</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1385</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1056</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>430</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1302</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1194</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1003</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>818</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3504,13 +3636,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Casseli Layza" refreshedDate="46133.932331249998" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="2688" xr:uid="{1C2E7FAE-0576-4AC9-AAFD-F52357483770}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Casseli Layza" refreshedDate="46144.413605671296" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="2928" xr:uid="{1C2E7FAE-0576-4AC9-AAFD-F52357483770}">
   <cacheSource type="worksheet">
     <worksheetSource name="TBRESUMEN"/>
   </cacheSource>
   <cacheFields count="6">
     <cacheField name="FECHA" numFmtId="14">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2025-12-01T00:00:00" maxDate="2026-04-22T00:00:00" count="134">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2025-12-01T00:00:00" maxDate="2026-05-03T00:00:00" count="144">
         <d v="2026-01-01T00:00:00"/>
         <d v="2026-01-02T00:00:00"/>
         <d v="2026-01-03T00:00:00"/>
@@ -3621,8 +3753,18 @@
         <d v="2026-04-18T00:00:00"/>
         <d v="2026-04-19T00:00:00"/>
         <d v="2026-04-20T00:00:00"/>
-        <m/>
         <d v="2026-04-21T00:00:00"/>
+        <d v="2026-04-22T00:00:00"/>
+        <d v="2026-04-23T00:00:00"/>
+        <d v="2026-04-24T00:00:00"/>
+        <d v="2026-04-25T00:00:00"/>
+        <d v="2026-04-26T00:00:00"/>
+        <d v="2026-04-27T00:00:00"/>
+        <d v="2026-04-28T00:00:00"/>
+        <d v="2026-04-29T00:00:00"/>
+        <d v="2026-04-30T00:00:00"/>
+        <d v="2026-05-01T00:00:00"/>
+        <d v="2026-05-02T00:00:00"/>
         <d v="2025-12-01T00:00:00" u="1"/>
         <d v="2025-12-02T00:00:00" u="1"/>
         <d v="2025-12-03T00:00:00" u="1"/>
@@ -3648,20 +3790,21 @@
       </sharedItems>
     </cacheField>
     <cacheField name="AÑO" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2026" maxValue="2026"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2026" maxValue="2026"/>
     </cacheField>
     <cacheField name="MES" numFmtId="0">
-      <sharedItems containsBlank="1" count="6">
+      <sharedItems containsBlank="1" count="7">
         <s v="ENERO"/>
         <s v="FEBRERO"/>
         <s v="MARZO"/>
         <s v="ABRIL"/>
-        <m/>
+        <s v="MAYO"/>
+        <m u="1"/>
         <s v="DICIEMBRE" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="DIA" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="31" count="32">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="31" count="31">
         <n v="1"/>
         <n v="2"/>
         <n v="3"/>
@@ -3693,11 +3836,10 @@
         <n v="29"/>
         <n v="30"/>
         <n v="31"/>
-        <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="HORA" numFmtId="20">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="1899-12-30T00:00:00" maxDate="1899-12-31T00:00:00" count="25">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="1899-12-30T00:00:00" maxDate="1899-12-31T00:00:00" count="24">
         <d v="1899-12-30T00:00:00"/>
         <d v="1899-12-30T01:00:00"/>
         <d v="1899-12-30T02:00:00"/>
@@ -3722,11 +3864,10 @@
         <d v="1899-12-30T21:00:00"/>
         <d v="1899-12-30T22:00:00"/>
         <d v="1899-12-30T23:00:00"/>
-        <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="Cantidad" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="555"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="555"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -3738,7 +3879,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="2688">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="2928">
   <r>
     <x v="0"/>
     <n v="2026"/>
@@ -24861,206 +25002,14 @@
   </r>
   <r>
     <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="20"/>
+    <x v="0"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="110"/>
-    <m/>
-    <x v="4"/>
-    <x v="31"/>
-    <x v="24"/>
-    <m/>
-  </r>
-  <r>
-    <x v="111"/>
-    <n v="2026"/>
-    <x v="3"/>
-    <x v="20"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25068,7 +25017,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25076,7 +25025,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25084,7 +25033,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25092,7 +25041,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25100,7 +25049,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25108,7 +25057,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25116,7 +25065,7 @@
     <n v="32"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25124,7 +25073,7 @@
     <n v="18"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25132,7 +25081,7 @@
     <n v="129"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25140,7 +25089,7 @@
     <n v="125"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25148,7 +25097,7 @@
     <n v="179"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25156,7 +25105,7 @@
     <n v="101"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25164,7 +25113,7 @@
     <n v="105"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25172,7 +25121,7 @@
     <n v="161"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25180,7 +25129,7 @@
     <n v="150"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25188,7 +25137,7 @@
     <n v="148"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25196,7 +25145,7 @@
     <n v="81"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25204,7 +25153,7 @@
     <n v="62"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25212,7 +25161,7 @@
     <n v="16"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25220,7 +25169,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25228,7 +25177,7 @@
     <n v="0"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <n v="2026"/>
     <x v="3"/>
     <x v="20"/>
@@ -25236,10 +25185,2122 @@
     <n v="0"/>
   </r>
   <r>
+    <x v="110"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="20"/>
+    <x v="23"/>
+    <n v="0"/>
+  </r>
+  <r>
     <x v="111"/>
     <n v="2026"/>
     <x v="3"/>
+    <x v="21"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="3"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="4"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="6"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="7"/>
+    <n v="21"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="8"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="9"/>
+    <n v="139"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="10"/>
+    <n v="175"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="11"/>
+    <n v="100"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="12"/>
+    <n v="100"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="13"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="14"/>
+    <n v="111"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="15"/>
+    <n v="106"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="16"/>
+    <n v="112"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="17"/>
+    <n v="78"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="18"/>
+    <n v="37"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="19"/>
+    <n v="9"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
     <x v="20"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="21"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="22"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="23"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="0"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="3"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="4"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="6"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="7"/>
+    <n v="22"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="8"/>
+    <n v="37"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="9"/>
+    <n v="285"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="10"/>
+    <n v="182"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="11"/>
+    <n v="122"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="12"/>
+    <n v="128"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="13"/>
+    <n v="114"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="14"/>
+    <n v="108"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="15"/>
+    <n v="125"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="16"/>
+    <n v="202"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="17"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="18"/>
+    <n v="19"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="19"/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="20"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="21"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="22"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="23"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="3"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="4"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="6"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="7"/>
+    <n v="29"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="8"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="9"/>
+    <n v="121"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="10"/>
+    <n v="142"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="11"/>
+    <n v="124"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="12"/>
+    <n v="115"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="13"/>
+    <n v="93"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="14"/>
+    <n v="133"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="15"/>
+    <n v="100"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="16"/>
+    <n v="84"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="17"/>
+    <n v="65"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="18"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="19"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="20"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="21"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="22"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="23"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="3"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="4"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="6"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="7"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="8"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="9"/>
+    <n v="71"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="10"/>
+    <n v="69"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="11"/>
+    <n v="113"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="12"/>
+    <n v="82"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="13"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="14"/>
+    <n v="22"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="15"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="16"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="17"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="18"/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="19"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="20"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="21"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="22"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="23"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="3"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="4"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="6"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="7"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="8"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="9"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="10"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="11"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="12"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="13"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="14"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="15"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="16"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="17"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="18"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="19"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="20"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="21"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="22"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="23"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="3"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="4"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="6"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="7"/>
+    <n v="44"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="8"/>
+    <n v="24"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="9"/>
+    <n v="129"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="10"/>
+    <n v="153"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="11"/>
+    <n v="198"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="12"/>
+    <n v="200"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="13"/>
+    <n v="86"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="14"/>
+    <n v="128"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="15"/>
+    <n v="106"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="16"/>
+    <n v="138"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="17"/>
+    <n v="54"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="18"/>
+    <n v="30"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="19"/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="20"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="21"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="22"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="23"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="3"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="4"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="6"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="7"/>
+    <n v="46"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="8"/>
+    <n v="33"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="9"/>
+    <n v="130"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="10"/>
+    <n v="140"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="11"/>
+    <n v="100"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="12"/>
+    <n v="197"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="13"/>
+    <n v="89"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="14"/>
+    <n v="95"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="15"/>
+    <n v="138"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="16"/>
+    <n v="156"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="17"/>
+    <n v="39"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="18"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="19"/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="20"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="21"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="22"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="23"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="3"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="4"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="6"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="7"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="8"/>
+    <n v="27"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="9"/>
+    <n v="59"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="10"/>
+    <n v="86"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="11"/>
+    <n v="150"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="12"/>
+    <n v="109"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="13"/>
+    <n v="103"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="14"/>
+    <n v="134"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="15"/>
+    <n v="144"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="16"/>
+    <n v="100"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="17"/>
+    <n v="49"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="18"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="19"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="20"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="21"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="22"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="23"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="3"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="4"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="6"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="7"/>
+    <n v="29"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="8"/>
+    <n v="27"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="9"/>
+    <n v="75"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="10"/>
+    <n v="112"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="11"/>
+    <n v="110"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="12"/>
+    <n v="79"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="13"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="14"/>
+    <n v="63"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="15"/>
+    <n v="96"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="16"/>
+    <n v="77"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="17"/>
+    <n v="56"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="18"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="19"/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="20"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="21"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="22"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="23"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="7"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="8"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="9"/>
+    <n v="9"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="10"/>
+    <n v="11"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="11"/>
+    <n v="9"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="12"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="13"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="14"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="15"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="16"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="17"/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="18"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="19"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="20"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="21"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="22"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="23"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="6"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="7"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="8"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="9"/>
+    <n v="136"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="10"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="11"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="12"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="13"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="14"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="15"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="16"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="17"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="18"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="19"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="20"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="21"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="22"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <x v="1"/>
     <x v="23"/>
     <n v="0"/>
   </r>
@@ -25253,20 +27314,21 @@
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
-      <items count="7">
+      <items count="8">
         <item h="1" x="0"/>
         <item h="1" x="1"/>
         <item h="1" x="2"/>
-        <item x="3"/>
+        <item h="1" x="3"/>
+        <item x="4"/>
+        <item h="1" m="1" x="6"/>
         <item h="1" m="1" x="5"/>
-        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0">
-      <items count="33">
+      <items count="32">
         <item h="1" x="0"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item h="1" x="2"/>
         <item h="1" x="3"/>
         <item h="1" x="4"/>
@@ -25285,7 +27347,7 @@
         <item h="1" x="17"/>
         <item h="1" x="18"/>
         <item h="1" x="19"/>
-        <item x="20"/>
+        <item h="1" x="20"/>
         <item h="1" x="21"/>
         <item h="1" x="22"/>
         <item h="1" x="23"/>
@@ -25296,12 +27358,18 @@
         <item h="1" x="28"/>
         <item h="1" x="29"/>
         <item h="1" x="30"/>
-        <item h="1" x="31"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="26">
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="25">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
         <item x="7"/>
         <item x="8"/>
         <item x="9"/>
@@ -25319,14 +27387,6 @@
         <item x="21"/>
         <item x="22"/>
         <item x="23"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="24"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -25419,16 +27479,16 @@
     <dataField name="Suma de Cantidad" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="13">
+    <format dxfId="39">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="38">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="37">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="23">
@@ -25437,7 +27497,6 @@
             <x v="2"/>
             <x v="3"/>
             <x v="4"/>
-            <x v="5"/>
             <x v="6"/>
             <x v="7"/>
             <x v="8"/>
@@ -25452,6 +27511,7 @@
             <x v="17"/>
             <x v="18"/>
             <x v="19"/>
+            <x v="20"/>
             <x v="21"/>
             <x v="22"/>
             <x v="23"/>
@@ -25459,10 +27519,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="9">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -25491,20 +27551,10 @@
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F64B669-1B30-4C42-82B1-4A3E70D5CF37}" name="TablaDinámica25" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12" rowHeaderCaption="FECHA">
-  <location ref="H5:I27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="H5:I36" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" numFmtId="14" showAll="0">
-      <items count="135">
-        <item m="1" x="112"/>
-        <item m="1" x="113"/>
-        <item m="1" x="114"/>
-        <item m="1" x="115"/>
-        <item m="1" x="116"/>
-        <item m="1" x="117"/>
-        <item m="1" x="118"/>
-        <item m="1" x="119"/>
-        <item m="1" x="120"/>
-        <item m="1" x="121"/>
+      <items count="145">
         <item m="1" x="122"/>
         <item m="1" x="123"/>
         <item m="1" x="124"/>
@@ -25517,6 +27567,16 @@
         <item m="1" x="131"/>
         <item m="1" x="132"/>
         <item m="1" x="133"/>
+        <item m="1" x="134"/>
+        <item m="1" x="135"/>
+        <item m="1" x="136"/>
+        <item m="1" x="137"/>
+        <item m="1" x="138"/>
+        <item m="1" x="139"/>
+        <item m="1" x="140"/>
+        <item m="1" x="141"/>
+        <item m="1" x="142"/>
+        <item m="1" x="143"/>
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -25627,25 +27687,36 @@
         <item x="107"/>
         <item x="108"/>
         <item x="109"/>
+        <item x="110"/>
         <item x="111"/>
-        <item x="110"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
-      <items count="7">
+      <items count="8">
         <item h="1" x="0"/>
         <item h="1" x="1"/>
         <item h="1" x="2"/>
         <item x="3"/>
+        <item h="1" x="4"/>
+        <item h="1" m="1" x="6"/>
         <item h="1" m="1" x="5"/>
-        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0">
-      <items count="33">
+      <items count="32">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -25677,7 +27748,6 @@
         <item x="28"/>
         <item x="29"/>
         <item x="30"/>
-        <item x="31"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -25687,7 +27757,7 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="22">
+  <rowItems count="31">
     <i>
       <x v="112"/>
     </i>
@@ -25751,6 +27821,33 @@
     <i>
       <x v="132"/>
     </i>
+    <i>
+      <x v="133"/>
+    </i>
+    <i>
+      <x v="134"/>
+    </i>
+    <i>
+      <x v="135"/>
+    </i>
+    <i>
+      <x v="136"/>
+    </i>
+    <i>
+      <x v="137"/>
+    </i>
+    <i>
+      <x v="138"/>
+    </i>
+    <i>
+      <x v="139"/>
+    </i>
+    <i>
+      <x v="140"/>
+    </i>
+    <i>
+      <x v="141"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -25809,28 +27906,28 @@
   </pivotTables>
   <data>
     <tabular pivotCacheId="1548459532">
-      <items count="32">
+      <items count="31">
         <i x="0"/>
-        <i x="1"/>
-        <i x="2"/>
-        <i x="3"/>
-        <i x="4"/>
-        <i x="5"/>
-        <i x="6"/>
-        <i x="7"/>
-        <i x="8"/>
-        <i x="9"/>
-        <i x="10"/>
-        <i x="11"/>
-        <i x="12"/>
-        <i x="13"/>
-        <i x="14"/>
-        <i x="15"/>
-        <i x="16"/>
-        <i x="17"/>
-        <i x="18"/>
-        <i x="19"/>
-        <i x="20" s="1"/>
+        <i x="1" s="1"/>
+        <i x="2" nd="1"/>
+        <i x="3" nd="1"/>
+        <i x="4" nd="1"/>
+        <i x="5" nd="1"/>
+        <i x="6" nd="1"/>
+        <i x="7" nd="1"/>
+        <i x="8" nd="1"/>
+        <i x="9" nd="1"/>
+        <i x="10" nd="1"/>
+        <i x="11" nd="1"/>
+        <i x="12" nd="1"/>
+        <i x="13" nd="1"/>
+        <i x="14" nd="1"/>
+        <i x="15" nd="1"/>
+        <i x="16" nd="1"/>
+        <i x="17" nd="1"/>
+        <i x="18" nd="1"/>
+        <i x="19" nd="1"/>
+        <i x="20" nd="1"/>
         <i x="21" nd="1"/>
         <i x="22" nd="1"/>
         <i x="23" nd="1"/>
@@ -25841,7 +27938,6 @@
         <i x="28" nd="1"/>
         <i x="29" nd="1"/>
         <i x="30" nd="1"/>
-        <i x="31" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -25855,13 +27951,14 @@
   </pivotTables>
   <data>
     <tabular pivotCacheId="1548459532">
-      <items count="6">
+      <items count="7">
         <i x="0"/>
         <i x="1"/>
         <i x="2"/>
-        <i x="3" s="1"/>
+        <i x="3"/>
+        <i x="4" s="1"/>
+        <i x="6" nd="1"/>
         <i x="5" nd="1"/>
-        <i x="4" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -25875,7 +27972,7 @@
   </pivotTables>
   <data>
     <tabular pivotCacheId="1548459532">
-      <items count="32">
+      <items count="31">
         <i x="0" s="1"/>
         <i x="1" s="1"/>
         <i x="2" s="1"/>
@@ -25897,17 +27994,16 @@
         <i x="18" s="1"/>
         <i x="19" s="1"/>
         <i x="20" s="1"/>
-        <i x="21" s="1" nd="1"/>
-        <i x="22" s="1" nd="1"/>
-        <i x="23" s="1" nd="1"/>
-        <i x="24" s="1" nd="1"/>
-        <i x="25" s="1" nd="1"/>
-        <i x="26" s="1" nd="1"/>
-        <i x="27" s="1" nd="1"/>
-        <i x="28" s="1" nd="1"/>
-        <i x="29" s="1" nd="1"/>
+        <i x="21" s="1"/>
+        <i x="22" s="1"/>
+        <i x="23" s="1"/>
+        <i x="24" s="1"/>
+        <i x="25" s="1"/>
+        <i x="26" s="1"/>
+        <i x="27" s="1"/>
+        <i x="28" s="1"/>
+        <i x="29" s="1"/>
         <i x="30" s="1" nd="1"/>
-        <i x="31" s="1" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -25921,13 +28017,14 @@
   </pivotTables>
   <data>
     <tabular pivotCacheId="1548459532">
-      <items count="6">
+      <items count="7">
         <i x="0"/>
         <i x="1"/>
         <i x="2"/>
         <i x="3" s="1"/>
+        <i x="4"/>
+        <i x="6" nd="1"/>
         <i x="5" nd="1"/>
-        <i x="4" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -25936,8 +28033,8 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="DIA" xr10:uid="{24C2ED56-5EE7-42DC-B4E3-F20905FDA00B}" cache="SegmentaciónDeDatos_DIA" caption="DIA" startItem="13" rowHeight="228600"/>
-  <slicer name="MES" xr10:uid="{AEEAFA48-0125-462C-91B2-0AF7574C1814}" cache="SegmentaciónDeDatos_MES" caption="MES" rowHeight="228600"/>
+  <slicer name="DIA" xr10:uid="{24C2ED56-5EE7-42DC-B4E3-F20905FDA00B}" cache="SegmentaciónDeDatos_DIA" caption="DIA" startItem="20" rowHeight="228600"/>
+  <slicer name="MES" xr10:uid="{AEEAFA48-0125-462C-91B2-0AF7574C1814}" cache="SegmentaciónDeDatos_MES" caption="MES" startItem="2" rowHeight="228600"/>
 </slicers>
 </file>
 
@@ -25949,15 +28046,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{785E938A-DD83-44EB-8612-1F46419DD23C}" name="TBRESUMEN" displayName="TBRESUMEN" ref="A5:F2669" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="A5:F2669" xr:uid="{785E938A-DD83-44EB-8612-1F46419DD23C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{785E938A-DD83-44EB-8612-1F46419DD23C}" name="TBRESUMEN" displayName="TBRESUMEN" ref="A5:F2933" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+  <autoFilter ref="A5:F2933" xr:uid="{785E938A-DD83-44EB-8612-1F46419DD23C}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{AA03A56E-BE6E-44BD-8664-0BE5E7E8EC5C}" name="FECHA" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{F392B1E8-81BF-4618-99C5-63CFF80F9BE5}" name="AÑO" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{2CF8B524-5A6E-4C4C-8659-5EC25E28EABE}" name="MES" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{3740A5C0-233F-4752-A308-55D65365E6F0}" name="DIA" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{724991CC-97B3-4E4E-A1EB-9B8303442499}" name="HORA" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{BBD02E23-3878-488A-ADD6-68A4C8637607}" name="Cantidad" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{AA03A56E-BE6E-44BD-8664-0BE5E7E8EC5C}" name="FECHA" dataDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{F392B1E8-81BF-4618-99C5-63CFF80F9BE5}" name="AÑO" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{2CF8B524-5A6E-4C4C-8659-5EC25E28EABE}" name="MES" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{3740A5C0-233F-4752-A308-55D65365E6F0}" name="DIA" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{724991CC-97B3-4E4E-A1EB-9B8303442499}" name="HORA" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{BBD02E23-3878-488A-ADD6-68A4C8637607}" name="Cantidad" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -25968,12 +28065,12 @@
   <autoFilter ref="A5:F1708" xr:uid="{785E938A-DD83-44EB-8612-1F46419DD23C}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{7D5CE986-03DE-4336-8DE6-10EE2FA4B5F2}" name="FECHA"/>
-    <tableColumn id="9" xr3:uid="{0FB34336-64F8-49F1-83FC-84A5CC0A6D3C}" name="AÑO" dataDxfId="15">
+    <tableColumn id="9" xr3:uid="{0FB34336-64F8-49F1-83FC-84A5CC0A6D3C}" name="AÑO" dataDxfId="25">
       <calculatedColumnFormula>YEAR(TBRESUMEN3[[#This Row],[FECHA]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{11A2B8AE-7AF3-4590-AF5E-6B075F8D4479}" name="MES"/>
     <tableColumn id="3" xr3:uid="{543B0EF0-62F6-461E-AEB3-23686CCF9AEA}" name="DIA"/>
-    <tableColumn id="4" xr3:uid="{EC35CD38-5F7B-4AC8-ADB3-30881E726247}" name="HORA" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{EC35CD38-5F7B-4AC8-ADB3-30881E726247}" name="HORA" dataDxfId="24"/>
     <tableColumn id="5" xr3:uid="{A5918A95-B5A3-4D43-B89A-E76A6B9EB015}" name="Cantidad"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -26297,7 +28394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDBBB223-C1D1-4222-ADC8-76C1132D0D0A}">
-  <dimension ref="A4:R2669"/>
+  <dimension ref="A4:R2933"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4609375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.921875" style="13" bestFit="1" customWidth="1"/>
@@ -26370,10 +28467,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="15">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="I6" s="13">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="I6" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -26396,10 +28493,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="15">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="I7" s="13">
-        <v>18</v>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="I7" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -26422,10 +28519,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="15">
-        <v>0.375</v>
-      </c>
-      <c r="I8" s="13">
-        <v>129</v>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="I8" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -26448,10 +28545,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="15">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="I9" s="13">
-        <v>125</v>
+        <v>0.125</v>
+      </c>
+      <c r="I9" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -26474,10 +28571,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="15">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="I10" s="13">
-        <v>179</v>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="I10" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -26500,10 +28597,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="I11" s="13">
-        <v>101</v>
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="I11" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -26526,10 +28623,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="15">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="I12" s="13">
-        <v>105</v>
+        <v>0.25</v>
+      </c>
+      <c r="I12" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -26552,10 +28649,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="15">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="I13" s="13">
-        <v>161</v>
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="I13" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -26578,10 +28675,10 @@
         <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>0.625</v>
-      </c>
-      <c r="I14" s="13">
-        <v>150</v>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="I14" s="17">
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -26604,10 +28701,10 @@
         <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="I15" s="13">
-        <v>148</v>
+        <v>0.375</v>
+      </c>
+      <c r="I15" s="17">
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -26630,10 +28727,10 @@
         <v>1</v>
       </c>
       <c r="H16" s="15">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="I16" s="13">
-        <v>81</v>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I16" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -26656,10 +28753,10 @@
         <v>1</v>
       </c>
       <c r="H17" s="15">
-        <v>0.75</v>
-      </c>
-      <c r="I17" s="13">
-        <v>62</v>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="I17" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -26682,10 +28779,10 @@
         <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="I18" s="13">
-        <v>16</v>
+        <v>0.5</v>
+      </c>
+      <c r="I18" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -26708,9 +28805,9 @@
         <v>0</v>
       </c>
       <c r="H19" s="15">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="I19" s="13">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="I19" s="17">
         <v>0</v>
       </c>
     </row>
@@ -26734,9 +28831,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="15">
-        <v>0.875</v>
-      </c>
-      <c r="I20" s="13">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I20" s="17">
         <v>0</v>
       </c>
     </row>
@@ -26760,9 +28857,9 @@
         <v>1</v>
       </c>
       <c r="H21" s="15">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="I21" s="13">
+        <v>0.625</v>
+      </c>
+      <c r="I21" s="17">
         <v>0</v>
       </c>
     </row>
@@ -26786,9 +28883,9 @@
         <v>0</v>
       </c>
       <c r="H22" s="15">
-        <v>0.95833333333333337</v>
-      </c>
-      <c r="I22" s="13">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I22" s="17">
         <v>0</v>
       </c>
     </row>
@@ -26812,9 +28909,9 @@
         <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="I23" s="13">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="I23" s="17">
         <v>0</v>
       </c>
     </row>
@@ -26838,9 +28935,9 @@
         <v>0</v>
       </c>
       <c r="H24" s="15">
-        <v>0.125</v>
-      </c>
-      <c r="I24" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="I24" s="17">
         <v>0</v>
       </c>
     </row>
@@ -26864,9 +28961,9 @@
         <v>1</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
-      </c>
-      <c r="I25" s="13">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="I25" s="17">
         <v>0</v>
       </c>
     </row>
@@ -26890,9 +28987,9 @@
         <v>0</v>
       </c>
       <c r="H26" s="15">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="I26" s="13">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I26" s="17">
         <v>0</v>
       </c>
     </row>
@@ -26916,9 +29013,9 @@
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>0.25</v>
-      </c>
-      <c r="I27" s="13">
+        <v>0.875</v>
+      </c>
+      <c r="I27" s="17">
         <v>0</v>
       </c>
     </row>
@@ -26942,9 +29039,9 @@
         <v>0</v>
       </c>
       <c r="H28" s="15">
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="I28" s="13">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="I28" s="17">
         <v>0</v>
       </c>
     </row>
@@ -26968,9 +29065,9 @@
         <v>0</v>
       </c>
       <c r="H29" s="15">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="I29" s="13">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="I29" s="17">
         <v>0</v>
       </c>
     </row>
@@ -26996,8 +29093,8 @@
       <c r="H30" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="I30" s="13">
-        <v>1307</v>
+      <c r="I30" s="17">
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -79779,6 +81876,5286 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="F2669" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2670" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2670" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2670" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2670" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2670" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2670" s="16">
+        <v>0</v>
+      </c>
+      <c r="F2670" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2671" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2671" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2671" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2671" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2671" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2671" s="16">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F2671" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2672" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2672" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2672" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2672" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2672" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2672" s="16">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F2672" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2673" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2673" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2673" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2673" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2673" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2673" s="16">
+        <v>0.125</v>
+      </c>
+      <c r="F2673" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2674" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2674" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2674" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2674" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2674" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2674" s="16">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F2674" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2675" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2675" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2675" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2675" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2675" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2675" s="16">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F2675" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2676" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2676" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2676" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2676" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2676" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2676" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="F2676" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2677" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2677" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2677" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2677" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2677" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2677" s="16">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F2677" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2678" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2678" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2678" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2678" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2678" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2678" s="16">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F2678" s="13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2679" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2679" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2679" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2679" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2679" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2679" s="16">
+        <v>0.375</v>
+      </c>
+      <c r="F2679" s="13">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2680" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2680" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2680" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2680" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2680" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2680" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F2680" s="13">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2681" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2681" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2681" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2681" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2681" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2681" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F2681" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2682" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2682" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2682" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2682" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2682" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2682" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F2682" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2683" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2683" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2683" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2683" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2683" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2683" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F2683" s="13">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2684" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2684" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2684" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2684" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2684" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2684" s="16">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F2684" s="13">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2685" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2685" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2685" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2685" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2685" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2685" s="16">
+        <v>0.625</v>
+      </c>
+      <c r="F2685" s="13">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2686" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2686" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2686" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2686" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2686" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2686" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2686" s="13">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2687" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2687" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2687" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2687" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2687" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2687" s="16">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F2687" s="13">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2688" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2688" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2688" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2688" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2688" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2688" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="F2688" s="13">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2689" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2689" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2689" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2689" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2689" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2689" s="16">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F2689" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2690" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2690" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2690" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2690" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2690" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2690" s="16">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F2690" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2691" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2691" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2691" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2691" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2691" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2691" s="16">
+        <v>0.875</v>
+      </c>
+      <c r="F2691" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2692" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2692" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2692" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2692" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2692" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2692" s="16">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F2692" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2693" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2693" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B2693" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2693" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2693" s="13">
+        <v>22</v>
+      </c>
+      <c r="E2693" s="16">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F2693" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2694" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2694" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2694" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2694" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2694" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2694" s="16">
+        <v>0</v>
+      </c>
+      <c r="F2694" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2695" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2695" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2695" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2695" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2695" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2695" s="16">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F2695" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2696" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2696" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2696" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2696" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2696" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2696" s="16">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F2696" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2697" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2697" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2697" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2697" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2697" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2697" s="16">
+        <v>0.125</v>
+      </c>
+      <c r="F2697" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2698" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2698" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2698" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2698" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2698" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2698" s="16">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F2698" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2699" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2699" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2699" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2699" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2699" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2699" s="16">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F2699" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2700" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2700" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2700" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2700" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2700" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2700" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="F2700" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2701" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2701" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2701" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2701" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2701" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2701" s="16">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F2701" s="13">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2702" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2702" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2702" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2702" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2702" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2702" s="16">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F2702" s="13">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2703" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2703" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2703" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2703" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2703" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2703" s="16">
+        <v>0.375</v>
+      </c>
+      <c r="F2703" s="13">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="2704" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2704" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2704" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2704" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2704" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2704" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F2704" s="13">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2705" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2705" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2705" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2705" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2705" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2705" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F2705" s="13">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2706" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2706" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2706" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2706" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2706" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2706" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F2706" s="13">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2707" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2707" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2707" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2707" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2707" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2707" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F2707" s="13">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2708" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2708" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2708" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2708" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2708" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2708" s="16">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F2708" s="13">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2709" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2709" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2709" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2709" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2709" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2709" s="16">
+        <v>0.625</v>
+      </c>
+      <c r="F2709" s="13">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2710" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2710" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2710" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2710" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2710" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2710" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2710" s="13">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2711" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2711" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2711" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2711" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2711" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2711" s="16">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F2711" s="13">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2712" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2712" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2712" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2712" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2712" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2712" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="F2712" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2713" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2713" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2713" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2713" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2713" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2713" s="16">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F2713" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2714" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2714" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2714" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2714" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2714" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2714" s="16">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F2714" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2715" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2715" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2715" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2715" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2715" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2715" s="16">
+        <v>0.875</v>
+      </c>
+      <c r="F2715" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2716" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2716" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2716" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2716" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2716" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2716" s="16">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F2716" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2717" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2717" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B2717" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2717" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2717" s="13">
+        <v>23</v>
+      </c>
+      <c r="E2717" s="16">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F2717" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2718" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2718" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2718" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2718" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2718" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2718" s="16">
+        <v>0</v>
+      </c>
+      <c r="F2718" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2719" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2719" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2719" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2719" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2719" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2719" s="16">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F2719" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2720" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2720" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2720" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2720" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2720" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2720" s="16">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F2720" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2721" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2721" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2721" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2721" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2721" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2721" s="16">
+        <v>0.125</v>
+      </c>
+      <c r="F2721" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2722" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2722" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2722" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2722" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2722" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2722" s="16">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F2722" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2723" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2723" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2723" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2723" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2723" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2723" s="16">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F2723" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2724" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2724" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2724" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2724" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2724" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2724" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="F2724" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2725" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2725" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2725" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2725" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2725" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2725" s="16">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F2725" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2726" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2726" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2726" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2726" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2726" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2726" s="16">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F2726" s="13">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2727" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2727" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2727" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2727" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2727" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2727" s="16">
+        <v>0.375</v>
+      </c>
+      <c r="F2727" s="13">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2728" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2728" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2728" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2728" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2728" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2728" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F2728" s="13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2729" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2729" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2729" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2729" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2729" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2729" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F2729" s="13">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2730" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2730" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2730" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2730" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2730" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2730" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F2730" s="13">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2731" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2731" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2731" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2731" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2731" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2731" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F2731" s="13">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2732" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2732" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2732" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2732" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2732" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2732" s="16">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F2732" s="13">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2733" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2733" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2733" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2733" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2733" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2733" s="16">
+        <v>0.625</v>
+      </c>
+      <c r="F2733" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2734" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2734" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2734" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2734" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2734" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2734" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2734" s="13">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2735" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2735" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2735" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2735" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2735" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2735" s="16">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F2735" s="13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2736" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2736" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2736" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2736" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2736" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2736" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="F2736" s="13">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2737" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2737" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2737" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2737" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2737" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2737" s="16">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F2737" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2738" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2738" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2738" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2738" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2738" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2738" s="16">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F2738" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2739" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2739" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2739" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2739" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2739" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2739" s="16">
+        <v>0.875</v>
+      </c>
+      <c r="F2739" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2740" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2740" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2740" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2740" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2740" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2740" s="16">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F2740" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2741" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2741" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B2741" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2741" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2741" s="13">
+        <v>24</v>
+      </c>
+      <c r="E2741" s="16">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F2741" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2742" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2742" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2742" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2742" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2742" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2742" s="16">
+        <v>0</v>
+      </c>
+      <c r="F2742" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2743" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2743" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2743" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2743" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2743" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2743" s="16">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F2743" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2744" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2744" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2744" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2744" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2744" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2744" s="16">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F2744" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2745" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2745" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2745" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2745" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2745" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2745" s="16">
+        <v>0.125</v>
+      </c>
+      <c r="F2745" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2746" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2746" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2746" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2746" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2746" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2746" s="16">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F2746" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2747" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2747" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2747" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2747" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2747" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2747" s="16">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F2747" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2748" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2748" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2748" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2748" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2748" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2748" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="F2748" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2749" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2749" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2749" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2749" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2749" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2749" s="16">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F2749" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2750" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2750" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2750" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2750" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2750" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2750" s="16">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F2750" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2751" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2751" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2751" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2751" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2751" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2751" s="16">
+        <v>0.375</v>
+      </c>
+      <c r="F2751" s="13">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2752" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2752" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2752" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2752" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2752" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2752" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F2752" s="13">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2753" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2753" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2753" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2753" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2753" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2753" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F2753" s="13">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2754" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2754" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2754" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2754" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2754" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2754" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F2754" s="13">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2755" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2755" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2755" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2755" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2755" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2755" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F2755" s="13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2756" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2756" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2756" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2756" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2756" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2756" s="16">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F2756" s="13">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2757" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2757" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2757" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2757" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2757" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2757" s="16">
+        <v>0.625</v>
+      </c>
+      <c r="F2757" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2758" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2758" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2758" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2758" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2758" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2758" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2758" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2759" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2759" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2759" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2759" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2759" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2759" s="16">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F2759" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2760" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2760" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2760" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2760" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2760" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2760" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="F2760" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2761" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2761" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2761" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2761" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2761" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2761" s="16">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F2761" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2762" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2762" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2762" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2762" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2762" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2762" s="16">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F2762" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2763" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2763" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2763" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2763" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2763" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2763" s="16">
+        <v>0.875</v>
+      </c>
+      <c r="F2763" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2764" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2764" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2764" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2764" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2764" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2764" s="16">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F2764" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2765" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2765" s="4">
+        <v>46137</v>
+      </c>
+      <c r="B2765" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2765" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2765" s="13">
+        <v>25</v>
+      </c>
+      <c r="E2765" s="16">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F2765" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2766" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2766" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2766" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2766" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2766" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2766" s="16">
+        <v>0</v>
+      </c>
+      <c r="F2766" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2767" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2767" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2767" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2767" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2767" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2767" s="16">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F2767" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2768" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2768" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2768" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2768" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2768" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2768" s="16">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F2768" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2769" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2769" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2769" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2769" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2769" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2769" s="16">
+        <v>0.125</v>
+      </c>
+      <c r="F2769" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2770" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2770" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2770" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2770" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2770" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2770" s="16">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F2770" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2771" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2771" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2771" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2771" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2771" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2771" s="16">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F2771" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2772" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2772" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2772" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2772" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2772" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2772" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="F2772" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2773" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2773" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2773" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2773" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2773" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2773" s="16">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F2773" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2774" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2774" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2774" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2774" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2774" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2774" s="16">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F2774" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2775" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2775" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2775" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2775" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2775" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2775" s="16">
+        <v>0.375</v>
+      </c>
+      <c r="F2775" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2776" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2776" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2776" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2776" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2776" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2776" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F2776" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2777" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2777" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2777" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2777" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2777" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2777" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F2777" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2778" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2778" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2778" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2778" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2778" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2778" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F2778" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2779" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2779" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2779" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2779" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2779" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2779" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F2779" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2780" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2780" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2780" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2780" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2780" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2780" s="16">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F2780" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2781" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2781" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2781" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2781" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2781" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2781" s="16">
+        <v>0.625</v>
+      </c>
+      <c r="F2781" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2782" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2782" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2782" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2782" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2782" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2782" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2782" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2783" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2783" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2783" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2783" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2783" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2783" s="16">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F2783" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2784" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2784" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2784" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2784" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2784" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2784" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="F2784" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2785" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2785" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2785" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2785" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2785" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2785" s="16">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F2785" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2786" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2786" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2786" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2786" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2786" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2786" s="16">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F2786" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2787" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2787" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2787" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2787" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2787" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2787" s="16">
+        <v>0.875</v>
+      </c>
+      <c r="F2787" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2788" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2788" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2788" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2788" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2788" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2788" s="16">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F2788" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2789" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2789" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B2789" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2789" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2789" s="13">
+        <v>26</v>
+      </c>
+      <c r="E2789" s="16">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F2789" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2790" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2790" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2790" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2790" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2790" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2790" s="16">
+        <v>0</v>
+      </c>
+      <c r="F2790" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2791" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2791" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2791" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2791" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2791" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2791" s="16">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F2791" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2792" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2792" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2792" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2792" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2792" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2792" s="16">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F2792" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2793" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2793" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2793" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2793" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2793" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2793" s="16">
+        <v>0.125</v>
+      </c>
+      <c r="F2793" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2794" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2794" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2794" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2794" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2794" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2794" s="16">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F2794" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2795" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2795" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2795" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2795" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2795" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2795" s="16">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F2795" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2796" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2796" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2796" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2796" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2796" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2796" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="F2796" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2797" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2797" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2797" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2797" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2797" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2797" s="16">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F2797" s="13">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2798" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2798" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2798" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2798" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2798" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2798" s="16">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F2798" s="13">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2799" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2799" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2799" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2799" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2799" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2799" s="16">
+        <v>0.375</v>
+      </c>
+      <c r="F2799" s="13">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2800" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2800" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2800" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2800" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2800" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2800" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F2800" s="13">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2801" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2801" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2801" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2801" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2801" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2801" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F2801" s="13">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2802" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2802" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2802" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2802" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2802" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2802" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F2802" s="13">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2803" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2803" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2803" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2803" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2803" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2803" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F2803" s="13">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2804" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2804" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2804" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2804" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2804" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2804" s="16">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F2804" s="13">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2805" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2805" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2805" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2805" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2805" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2805" s="16">
+        <v>0.625</v>
+      </c>
+      <c r="F2805" s="13">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2806" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2806" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2806" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2806" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2806" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2806" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2806" s="13">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2807" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2807" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2807" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2807" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2807" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2807" s="16">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F2807" s="13">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2808" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2808" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2808" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2808" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2808" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2808" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="F2808" s="13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2809" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2809" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2809" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2809" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2809" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2809" s="16">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F2809" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2810" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2810" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2810" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2810" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2810" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2810" s="16">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F2810" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2811" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2811" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2811" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2811" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2811" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2811" s="16">
+        <v>0.875</v>
+      </c>
+      <c r="F2811" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2812" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2812" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2812" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2812" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2812" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2812" s="16">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F2812" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2813" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2813" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2813" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2813" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2813" s="13">
+        <v>27</v>
+      </c>
+      <c r="E2813" s="16">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F2813" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2814" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2814" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2814" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2814" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2814" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2814" s="16">
+        <v>0</v>
+      </c>
+      <c r="F2814" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2815" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2815" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2815" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2815" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2815" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2815" s="16">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F2815" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2816" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2816" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2816" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2816" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2816" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2816" s="16">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F2816" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2817" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2817" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2817" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2817" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2817" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2817" s="16">
+        <v>0.125</v>
+      </c>
+      <c r="F2817" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2818" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2818" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2818" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2818" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2818" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2818" s="16">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F2818" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2819" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2819" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2819" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2819" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2819" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2819" s="16">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F2819" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2820" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2820" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2820" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2820" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2820" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2820" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="F2820" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2821" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2821" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2821" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2821" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2821" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2821" s="16">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F2821" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2822" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2822" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2822" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2822" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2822" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2822" s="16">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F2822" s="13">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2823" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2823" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2823" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2823" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2823" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2823" s="16">
+        <v>0.375</v>
+      </c>
+      <c r="F2823" s="13">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2824" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2824" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2824" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2824" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2824" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2824" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F2824" s="13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2825" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2825" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2825" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2825" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2825" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2825" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F2825" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2826" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2826" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2826" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2826" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2826" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2826" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F2826" s="13">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2827" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2827" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2827" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2827" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2827" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2827" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F2827" s="13">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2828" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2828" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2828" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2828" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2828" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2828" s="16">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F2828" s="13">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2829" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2829" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2829" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2829" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2829" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2829" s="16">
+        <v>0.625</v>
+      </c>
+      <c r="F2829" s="13">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2830" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2830" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2830" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2830" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2830" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2830" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2830" s="13">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2831" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2831" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2831" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2831" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2831" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2831" s="16">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F2831" s="13">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2832" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2832" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2832" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2832" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2832" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2832" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="F2832" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2833" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2833" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2833" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2833" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2833" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2833" s="16">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F2833" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2834" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2834" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2834" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2834" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2834" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2834" s="16">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F2834" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2835" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2835" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2835" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2835" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2835" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2835" s="16">
+        <v>0.875</v>
+      </c>
+      <c r="F2835" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2836" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2836" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2836" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2836" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2836" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2836" s="16">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F2836" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2837" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2837" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2837" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2837" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2837" s="13">
+        <v>28</v>
+      </c>
+      <c r="E2837" s="16">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F2837" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2838" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2838" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2838" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2838" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2838" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2838" s="16">
+        <v>0</v>
+      </c>
+      <c r="F2838" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2839" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2839" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2839" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2839" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2839" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2839" s="16">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F2839" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2840" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2840" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2840" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2840" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2840" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2840" s="16">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F2840" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2841" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2841" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2841" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2841" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2841" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2841" s="16">
+        <v>0.125</v>
+      </c>
+      <c r="F2841" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2842" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2842" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2842" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2842" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2842" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2842" s="16">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F2842" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2843" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2843" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2843" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2843" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2843" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2843" s="16">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F2843" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2844" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2844" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2844" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2844" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2844" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2844" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="F2844" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2845" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2845" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2845" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2845" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2845" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2845" s="16">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F2845" s="13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2846" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2846" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2846" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2846" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2846" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2846" s="16">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F2846" s="13">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2847" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2847" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2847" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2847" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2847" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2847" s="16">
+        <v>0.375</v>
+      </c>
+      <c r="F2847" s="13">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2848" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2848" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2848" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2848" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2848" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2848" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F2848" s="13">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2849" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2849" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2849" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2849" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2849" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2849" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F2849" s="13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2850" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2850" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2850" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2850" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2850" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2850" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F2850" s="13">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2851" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2851" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2851" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2851" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2851" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2851" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F2851" s="13">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2852" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2852" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2852" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2852" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2852" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2852" s="16">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F2852" s="13">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2853" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2853" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2853" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2853" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2853" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2853" s="16">
+        <v>0.625</v>
+      </c>
+      <c r="F2853" s="13">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2854" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2854" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2854" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2854" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2854" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2854" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2854" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2855" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2855" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2855" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2855" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2855" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2855" s="16">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F2855" s="13">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2856" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2856" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2856" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2856" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2856" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2856" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="F2856" s="13">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2857" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2857" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2857" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2857" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2857" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2857" s="16">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F2857" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2858" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2858" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2858" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2858" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2858" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2858" s="16">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F2858" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2859" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2859" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2859" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2859" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2859" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2859" s="16">
+        <v>0.875</v>
+      </c>
+      <c r="F2859" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2860" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2860" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2860" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2860" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2860" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2860" s="16">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F2860" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2861" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2861" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2861" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2861" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2861" s="13">
+        <v>29</v>
+      </c>
+      <c r="E2861" s="16">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F2861" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2862" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2862" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2862" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2862" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2862" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2862" s="16">
+        <v>0</v>
+      </c>
+      <c r="F2862" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2863" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2863" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2863" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2863" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2863" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2863" s="16">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F2863" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2864" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2864" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2864" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2864" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2864" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2864" s="16">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F2864" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2865" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2865" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2865" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2865" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2865" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2865" s="16">
+        <v>0.125</v>
+      </c>
+      <c r="F2865" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2866" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2866" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2866" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2866" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2866" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2866" s="16">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F2866" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2867" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2867" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2867" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2867" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2867" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2867" s="16">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F2867" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2868" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2868" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2868" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2868" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2868" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2868" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="F2868" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2869" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2869" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2869" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2869" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2869" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2869" s="16">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F2869" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2870" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2870" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2870" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2870" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2870" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2870" s="16">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F2870" s="13">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2871" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2871" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2871" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2871" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2871" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2871" s="16">
+        <v>0.375</v>
+      </c>
+      <c r="F2871" s="13">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2872" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2872" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2872" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2872" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2872" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2872" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F2872" s="13">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2873" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2873" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2873" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2873" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2873" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2873" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F2873" s="13">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2874" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2874" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2874" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2874" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2874" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2874" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F2874" s="13">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2875" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2875" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2875" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2875" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2875" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2875" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F2875" s="13">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2876" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2876" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2876" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2876" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2876" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2876" s="16">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F2876" s="13">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2877" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2877" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2877" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2877" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2877" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2877" s="16">
+        <v>0.625</v>
+      </c>
+      <c r="F2877" s="13">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2878" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2878" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2878" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2878" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2878" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2878" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2878" s="13">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2879" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2879" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2879" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2879" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2879" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2879" s="16">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F2879" s="13">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2880" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2880" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2880" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2880" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2880" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2880" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="F2880" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2881" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2881" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2881" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2881" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2881" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2881" s="16">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F2881" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2882" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2882" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2882" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2882" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2882" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2882" s="16">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F2882" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2883" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2883" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2883" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2883" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2883" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2883" s="16">
+        <v>0.875</v>
+      </c>
+      <c r="F2883" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2884" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2884" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2884" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2884" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2884" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2884" s="16">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F2884" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2885" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2885" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2885" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2885" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2885" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2885" s="16">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F2885" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2886" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2886" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2886" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2886" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2886" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2886" s="16">
+        <v>0</v>
+      </c>
+      <c r="F2886" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2887" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2887" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2887" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2887" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2887" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2887" s="16">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F2887" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2888" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2888" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2888" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2888" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2888" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2888" s="16">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F2888" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2889" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2889" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2889" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2889" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2889" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2889" s="16">
+        <v>0.125</v>
+      </c>
+      <c r="F2889" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2890" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2890" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2890" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2890" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2890" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2890" s="16">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F2890" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2891" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2891" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2891" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2891" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2891" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2891" s="16">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F2891" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2892" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2892" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2892" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2892" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2892" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2892" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="F2892" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2893" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2893" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2893" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2893" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2893" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2893" s="16">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F2893" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2894" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2894" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2894" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2894" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2894" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2894" s="16">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F2894" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2895" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2895" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2895" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2895" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2895" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2895" s="16">
+        <v>0.375</v>
+      </c>
+      <c r="F2895" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2896" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2896" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2896" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2896" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2896" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2896" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F2896" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2897" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2897" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2897" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2897" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2897" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2897" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F2897" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2898" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2898" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2898" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2898" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2898" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2898" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F2898" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2899" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2899" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2899" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2899" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2899" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2899" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F2899" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2900" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2900" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2900" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2900" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2900" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2900" s="16">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F2900" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2901" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2901" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2901" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2901" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2901" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2901" s="16">
+        <v>0.625</v>
+      </c>
+      <c r="F2901" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2902" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2902" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2902" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2902" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2902" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2902" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2902" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2903" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2903" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2903" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2903" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2903" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2903" s="16">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F2903" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2904" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2904" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2904" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2904" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2904" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2904" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="F2904" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2905" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2905" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2905" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2905" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2905" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2905" s="16">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F2905" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2906" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2906" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2906" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2906" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2906" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2906" s="16">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F2906" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2907" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2907" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2907" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2907" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2907" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2907" s="16">
+        <v>0.875</v>
+      </c>
+      <c r="F2907" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2908" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2908" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2908" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2908" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2908" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2908" s="16">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F2908" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2909" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2909" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2909" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2909" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2909" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2909" s="16">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F2909" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2910" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2910" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2910" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2910" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2910" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2910" s="16">
+        <v>0</v>
+      </c>
+      <c r="F2910" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2911" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2911" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2911" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2911" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2911" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2911" s="16">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F2911" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2912" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2912" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2912" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2912" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2912" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2912" s="16">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F2912" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2913" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2913" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2913" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2913" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2913" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2913" s="16">
+        <v>0.125</v>
+      </c>
+      <c r="F2913" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2914" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2914" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2914" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2914" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2914" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2914" s="16">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F2914" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2915" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2915" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2915" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2915" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2915" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2915" s="16">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F2915" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2916" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2916" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2916" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2916" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2916" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2916" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="F2916" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2917" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2917" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2917" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2917" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2917" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2917" s="16">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F2917" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2918" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2918" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2918" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2918" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2918" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2918" s="16">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F2918" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2919" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2919" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2919" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2919" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2919" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2919" s="16">
+        <v>0.375</v>
+      </c>
+      <c r="F2919" s="13">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2920" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2920" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2920" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2920" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2920" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2920" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F2920" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2921" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2921" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2921" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2921" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2921" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2921" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F2921" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2922" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2922" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2922" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2922" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2922" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2922" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F2922" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2923" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2923" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2923" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2923" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2923" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2923" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F2923" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2924" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2924" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2924" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2924" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2924" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2924" s="16">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F2924" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2925" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2925" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2925" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2925" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2925" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2925" s="16">
+        <v>0.625</v>
+      </c>
+      <c r="F2925" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2926" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2926" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2926" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2926" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2926" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2926" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2926" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2927" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2927" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2927" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2927" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2927" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2927" s="16">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F2927" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2928" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2928" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2928" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2928" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2928" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2928" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="F2928" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2929" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2929" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2929" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2929" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2929" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2929" s="16">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F2929" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2930" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2930" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2930" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2930" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2930" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2930" s="16">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F2930" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2931" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2931" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2931" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2931" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2931" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2931" s="16">
+        <v>0.875</v>
+      </c>
+      <c r="F2931" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2932" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2932" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2932" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2932" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2932" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2932" s="16">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F2932" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2933" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2933" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2933" s="13">
+        <v>2026</v>
+      </c>
+      <c r="C2933" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2933" s="13">
+        <v>2</v>
+      </c>
+      <c r="E2933" s="16">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F2933" s="13">
         <v>0</v>
       </c>
     </row>
@@ -80075,94 +87452,148 @@
     <row r="27" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A27" s="11"/>
       <c r="E27" s="1"/>
-      <c r="H27" s="12" t="s">
-        <v>4</v>
+      <c r="H27" s="12">
+        <v>46134</v>
       </c>
       <c r="I27">
-        <v>18196</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A28" s="11"/>
       <c r="E28" s="1"/>
+      <c r="H28" s="12">
+        <v>46135</v>
+      </c>
+      <c r="I28">
+        <v>1385</v>
+      </c>
     </row>
     <row r="29" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A29" s="11"/>
       <c r="E29" s="1"/>
+      <c r="H29" s="12">
+        <v>46136</v>
+      </c>
+      <c r="I29">
+        <v>1056</v>
+      </c>
     </row>
     <row r="30" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A30" s="11"/>
       <c r="E30" s="1"/>
+      <c r="H30" s="12">
+        <v>46137</v>
+      </c>
+      <c r="I30">
+        <v>430</v>
+      </c>
     </row>
     <row r="31" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A31" s="11"/>
       <c r="E31" s="1"/>
+      <c r="H31" s="12">
+        <v>46138</v>
+      </c>
+      <c r="I31">
+        <v>17</v>
+      </c>
     </row>
     <row r="32" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A32" s="11"/>
       <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="1:5" ht="14.6" x14ac:dyDescent="0.4">
+      <c r="H32" s="12">
+        <v>46139</v>
+      </c>
+      <c r="I32">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A33" s="11"/>
       <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="1:5" ht="14.6" x14ac:dyDescent="0.4">
+      <c r="H33" s="12">
+        <v>46140</v>
+      </c>
+      <c r="I33">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A34" s="11"/>
       <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:5" ht="14.6" x14ac:dyDescent="0.4">
+      <c r="H34" s="12">
+        <v>46141</v>
+      </c>
+      <c r="I34">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A35" s="11"/>
       <c r="E35" s="1"/>
-    </row>
-    <row r="36" spans="1:5" ht="14.6" x14ac:dyDescent="0.4">
+      <c r="H35" s="12">
+        <v>46142</v>
+      </c>
+      <c r="I35">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A36" s="11"/>
       <c r="E36" s="1"/>
-    </row>
-    <row r="37" spans="1:5" ht="14.6" x14ac:dyDescent="0.4">
+      <c r="H36" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="I36">
+        <v>26520</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A37" s="11"/>
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="1:5" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A38" s="11"/>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="1:5" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A39" s="11"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:5" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A40" s="11"/>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="1:5" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A41" s="11"/>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" spans="1:5" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A42" s="11"/>
       <c r="E42" s="1"/>
     </row>
-    <row r="43" spans="1:5" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A43" s="11"/>
       <c r="E43" s="1"/>
     </row>
-    <row r="44" spans="1:5" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A44" s="11"/>
       <c r="E44" s="1"/>
     </row>
-    <row r="45" spans="1:5" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A45" s="11"/>
       <c r="E45" s="1"/>
     </row>
-    <row r="46" spans="1:5" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A46" s="11"/>
       <c r="E46" s="1"/>
     </row>
-    <row r="47" spans="1:5" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A47" s="11"/>
       <c r="E47" s="1"/>
     </row>
-    <row r="48" spans="1:5" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:9" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A48" s="11"/>
       <c r="E48" s="1"/>
     </row>
